--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N76_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N76_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.05931946439534</v>
+        <v>8.947139412964244</v>
       </c>
       <c r="D2" t="n">
-        <v>54.57683083933339</v>
+        <v>8.868735011391676</v>
       </c>
       <c r="E2" t="n">
-        <v>13.60748587027939</v>
+        <v>2.2112164539204</v>
       </c>
       <c r="F2" t="n">
-        <v>13.68207640319902</v>
+        <v>2.223337415519841</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.81168516655453</v>
+        <v>5.169398839565111</v>
       </c>
       <c r="D3" t="n">
-        <v>31.66713788623517</v>
+        <v>5.145909906513215</v>
       </c>
       <c r="E3" t="n">
-        <v>13.60748587027939</v>
+        <v>2.2112164539204</v>
       </c>
       <c r="F3" t="n">
-        <v>13.68207640319902</v>
+        <v>2.223337415519841</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.87581566129306</v>
+        <v>6.967320044960123</v>
       </c>
       <c r="D4" t="n">
-        <v>42.82718383655292</v>
+        <v>6.95941737343985</v>
       </c>
       <c r="E4" t="n">
-        <v>13.60748587027939</v>
+        <v>2.2112164539204</v>
       </c>
       <c r="F4" t="n">
-        <v>13.68207640319902</v>
+        <v>2.223337415519841</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.57701598596322</v>
+        <v>3.668765097719023</v>
       </c>
       <c r="D5" t="n">
-        <v>22.06946206389731</v>
+        <v>3.586287585383313</v>
       </c>
       <c r="E5" t="n">
-        <v>13.60748587027939</v>
+        <v>2.2112164539204</v>
       </c>
       <c r="F5" t="n">
-        <v>13.68207640319902</v>
+        <v>2.223337415519841</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.56454616775983</v>
+        <v>3.666738752260973</v>
       </c>
       <c r="D6" t="n">
-        <v>22.45978351136404</v>
+        <v>3.649714820596656</v>
       </c>
       <c r="E6" t="n">
-        <v>13.60748587027939</v>
+        <v>2.2112164539204</v>
       </c>
       <c r="F6" t="n">
-        <v>13.68207640319902</v>
+        <v>2.223337415519841</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14.03236186413628</v>
+        <v>2.280258802922146</v>
       </c>
       <c r="D7" t="n">
-        <v>13.51227520675287</v>
+        <v>2.195744721097341</v>
       </c>
       <c r="E7" t="n">
-        <v>13.60748587027939</v>
+        <v>2.2112164539204</v>
       </c>
       <c r="F7" t="n">
-        <v>13.68207640319902</v>
+        <v>2.223337415519841</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.43567704690668</v>
+        <v>7.383297520122335</v>
       </c>
       <c r="D8" t="n">
-        <v>45.49479210350693</v>
+        <v>7.392903716819877</v>
       </c>
       <c r="E8" t="n">
-        <v>13.60748587027939</v>
+        <v>2.2112164539204</v>
       </c>
       <c r="F8" t="n">
-        <v>13.68207640319902</v>
+        <v>2.223337415519841</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>13.2527319652536</v>
+        <v>2.153568944353709</v>
       </c>
       <c r="D9" t="n">
-        <v>13.34170008333551</v>
+        <v>2.168026263542021</v>
       </c>
       <c r="E9" t="n">
-        <v>13.60748587027939</v>
+        <v>2.2112164539204</v>
       </c>
       <c r="F9" t="n">
-        <v>13.68207640319902</v>
+        <v>2.223337415519841</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>36.04976686957274</v>
+        <v>5.858087116305571</v>
       </c>
       <c r="D10" t="n">
-        <v>36.18028282755934</v>
+        <v>5.879295959478393</v>
       </c>
       <c r="E10" t="n">
-        <v>13.60748587027939</v>
+        <v>2.2112164539204</v>
       </c>
       <c r="F10" t="n">
-        <v>13.68207640319902</v>
+        <v>2.223337415519841</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>45.91818927982912</v>
+        <v>7.461705757972233</v>
       </c>
       <c r="D11" t="n">
-        <v>46.35628914004136</v>
+        <v>7.532896985256722</v>
       </c>
       <c r="E11" t="n">
-        <v>13.60748587027939</v>
+        <v>2.2112164539204</v>
       </c>
       <c r="F11" t="n">
-        <v>13.68207640319902</v>
+        <v>2.223337415519841</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.43463772689919</v>
+        <v>5.758128630621119</v>
       </c>
       <c r="D12" t="n">
-        <v>35.95890532857479</v>
+        <v>5.843322115893404</v>
       </c>
       <c r="E12" t="n">
-        <v>13.60748587027939</v>
+        <v>2.2112164539204</v>
       </c>
       <c r="F12" t="n">
-        <v>13.68207640319902</v>
+        <v>2.223337415519841</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>56.44116350919428</v>
+        <v>9.171689070244071</v>
       </c>
       <c r="D13" t="n">
-        <v>56.44116350919428</v>
+        <v>9.171689070244071</v>
       </c>
       <c r="E13" t="n">
-        <v>13.60748587027939</v>
+        <v>2.2112164539204</v>
       </c>
       <c r="F13" t="n">
-        <v>13.68207640319902</v>
+        <v>2.223337415519841</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>30.23333276210053</v>
+        <v>4.912916573841336</v>
       </c>
       <c r="D14" t="n">
-        <v>30.23333276210053</v>
+        <v>4.912916573841336</v>
       </c>
       <c r="E14" t="n">
-        <v>13.60748587027939</v>
+        <v>2.2112164539204</v>
       </c>
       <c r="F14" t="n">
-        <v>13.68207640319902</v>
+        <v>2.223337415519841</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
